--- a/erp-server/erp-server-oms/src/main/resources/excel/SoReturnExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoReturnExport.xlsx
@@ -776,7 +776,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -784,6 +784,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1233,7 +1236,7 @@
       <c r="O2" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="3" t="s">
         <v>34</v>
       </c>
       <c r="Q2" s="1" t="s">

--- a/erp-server/erp-server-oms/src/main/resources/excel/SoReturnExport.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/SoReturnExport.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t>退货订单号</t>
   </si>
@@ -113,6 +113,9 @@
   </si>
   <si>
     <t>{.deliveryQty}</t>
+  </si>
+  <si>
+    <t>{.unDeliveryQty}</t>
   </si>
   <si>
     <t>{.unit}</t>
@@ -1231,25 +1234,25 @@
         <v>32</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
